--- a/stories/arbres/ATOM-EMO.LEX.007-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Violette attend dans le salon. Des cousins vont arriver. Ses jambes bougent. Ses mains froissent le coussin. Violette dit : je suis nerveuse. Maman l'écoute. Maman dit : on peut demander une pause. Violette dit : je veux une pause. Elle s'assoit près de maman. Elle souffle. Les jambes se calment. Maman dit : nerveux, ce n'est pas vilain. Une pause, c'est bien.</t>
+          <t>Violette attend dans le salon. Des cousins vont arriver. Ses jambes bougent. Ses mains froissent le coussin. Je suis nerveuse. Maman l'écoute. On peut demander une pause. Je veux une pause. Elle s'assoit près de maman. Elle souffle. Les jambes se calment. Nerveux, ce n'est pas vilain. Une pause, c'est bien.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Violette attend dans le salon. Des cousins vont arriver. Ses jambes bougent. Ses mains froissent le coussin.
+enfant-f|Je suis nerveuse. Maman l'écoute.
+maman|On peut demander une pause.
+enfant-f|Je veux une pause.
+narrateur|Elle s'assoit près de maman. Elle souffle. Les jambes se calment.
+maman|Nerveux, ce n'est pas vilain.
+narrateur|Une pause, c'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Violette n'arrive pas à tenir. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Violette a nommé : nerveuse. Elle a demandé une pause. Elle s'est assise.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Violette pose les mains. Maman reste près d'elle.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Une pause, c'est bien.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Violette n'arrive pas à tenir. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Violette a nommé : nerveuse. Elle a demandé une pause. Elle s'est assise.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Violette pose les mains. Maman reste près d'elle.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.007-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Violette est nerveuse</t>
+          <t>Victorina demande une pause</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le gâteau sent le chocolat. Les cousins vont arriver. Victorina nomme nerveuse, demande une pause, s'assoit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Violette attend dans le salon. Des cousins vont arriver. Ses jambes bougent. Ses mains froissent le coussin. Je suis nerveuse. Maman l'écoute. On peut demander une pause. Je veux une pause. Elle s'assoit près de maman. Elle souffle. Les jambes se calment. Nerveux, ce n'est pas vilain. Une pause, c'est bien.</t>
+          <t>Le gâteau sent le chocolat. Il est encore un peu chaud. Trois assiettes attendent sur la table. Les fourchettes brillent à côté. La sonnette va bientôt sonner. Les cousins arrivent tout à l'heure. Le gâteau sent bon, Victorina. Il sent le chocolat. Oui. Il est encore tiède. Un napperon blanc est sous le plat. Il a de petits trous. Comme de la dentelle. Tu as vu les assiettes ? Il y en a trois. Oui. Pour plus tard. En ce moment, Victorina attend dans le salon. Elle est sur le canapé. Ses jambes bougent. Ses mains froissent le coussin. Le coussin fait un bruit de tissu. Je suis nerveuse. Mes jambes bougent. Je t'écoute. Nerveux, ce n'est pas vilain. On peut demander une pause. Je veux une pause. Oui, Victorina. On s'assoit. Elle s'assoit près de maman. Elle pose les pieds au tapis. Les pieds sont posés. Tu souffles avec moi ? Oui, maman. Victorina souffle. Les jambes se calment. Les mains laissent le coussin. Une pause, c'est bien. Bravo, Victorina. C'est du bon travail. Tu as demandé la pause ? Oui. Je suis nerveuse. Tu as nommé. Tu t'es assise. Le gâteau sent encore le chocolat. Les assiettes attendent, toutes calmes. La sonnette n'a pas sonné. On a le temps. Mes mains sont posées. Oui. Elles sont douces, maintenant. Tu restes près de moi ? Oui, maman. Le napperon blanc ne bouge plus. Une miette de chocolat brille sur le plat. On la laisse pour plus tard. Le gâteau est tiède. Oui. Comme tes mains. Victorina pose les mains sur ses genoux. Le canapé est mou sous elle. On attend ensemble. Ensemble. Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,79 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Violette attend dans le salon. Des cousins vont arriver. Ses jambes bougent. Ses mains froissent le coussin.
-enfant-f|Je suis nerveuse. Maman l'écoute.
+          <t>narrateur|Le gâteau sent le chocolat.
+narrateur|Il est encore un peu chaud.
+narrateur|Trois assiettes attendent sur la table.
+narrateur|Les fourchettes brillent à côté.
+narrateur|La sonnette va bientôt sonner.
+narrateur|Les cousins arrivent tout à l'heure.
+maman|Le gâteau sent bon, Victorina.
+enfant-f|Il sent le chocolat.
+maman|Oui.
+maman|Il est encore tiède.
+narrateur|Un napperon blanc est sous le plat.
+narrateur|Il a de petits trous.
+narrateur|Comme de la dentelle.
+maman|Tu as vu les assiettes ?
+enfant-f|Il y en a trois.
+maman|Oui.
+maman|Pour plus tard.
+narrateur|En ce moment, Victorina attend dans le salon.
+narrateur|Elle est sur le canapé.
+narrateur|Ses jambes bougent.
+narrateur|Ses mains froissent le coussin.
+narrateur|Le coussin fait un bruit de tissu.
+enfant-f|Je suis nerveuse.
+enfant-f|Mes jambes bougent.
+maman|Je t'écoute.
+maman|Nerveux, ce n'est pas vilain.
 maman|On peut demander une pause.
 enfant-f|Je veux une pause.
-narrateur|Elle s'assoit près de maman. Elle souffle. Les jambes se calment.
-maman|Nerveux, ce n'est pas vilain.
-narrateur|Une pause, c'est bien.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Oui, Victorina.
+maman|On s'assoit.
+narrateur|Elle s'assoit près de maman.
+narrateur|Elle pose les pieds au tapis.
+maman|Les pieds sont posés.
+maman|Tu souffles avec moi ?
+enfant-f|Oui, maman.
+narrateur|Victorina souffle.
+narrateur|Les jambes se calment.
+narrateur|Les mains laissent le coussin.
+maman|Une pause, c'est bien.
+maman|Bravo, Victorina.
+maman|C'est du bon travail.
+maman|Tu as demandé la pause ?
+enfant-f|Oui.
+enfant-f|Je suis nerveuse.
+maman|Tu as nommé.
+maman|Tu t'es assise.
+narrateur|Le gâteau sent encore le chocolat.
+narrateur|Les assiettes attendent, toutes calmes.
+maman|La sonnette n'a pas sonné.
+maman|On a le temps.
+enfant-f|Mes mains sont posées.
+maman|Oui.
+maman|Elles sont douces, maintenant.
+maman|Tu restes près de moi ?
+enfant-f|Oui, maman.
+narrateur|Le napperon blanc ne bouge plus.
+narrateur|Une miette de chocolat brille sur le plat.
+maman|On la laisse pour plus tard.
+enfant-f|Le gâteau est tiède.
+maman|Oui.
+maman|Comme tes mains.
+narrateur|Victorina pose les mains sur ses genoux.
+narrateur|Le canapé est mou sous elle.
+maman|On attend ensemble.
+enfant-f|Ensemble.
+maman|Oui.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cuisine_gateau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1421,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Violette n'arrive pas à tenir. Que fait-elle ?</t>
+          <t>Victorina n'arrive pas à tenir. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1577,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Violette n'arrive pas à tenir. Que fait-elle ?</t>
+          <t>narrateur|Victorina n'arrive pas à tenir.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Violette a nommé : nerveuse. Elle a demandé une pause. Elle s'est assise.</t>
+          <t>Victorina a nommé : nerveuse. Nerveux, on peut le dire. Elle a demandé une pause. Elle s'est assise. Bravo, Victorina. Tu as demandé une pause. C'est du bon travail. Je suis nerveuse. J'ai demandé une pause. Oui. Tu t'es assise. Les mains sont posées ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1750,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Violette a nommé : nerveuse. Elle a demandé une pause. Elle s'est assise.</t>
+          <t>narrateur|Victorina a nommé : nerveuse.
+narrateur|Nerveux, on peut le dire.
+narrateur|Elle a demandé une pause.
+narrateur|Elle s'est assise.
+maman|Bravo, Victorina.
+maman|Tu as demandé une pause.
+maman|C'est du bon travail.
+enfant-f|Je suis nerveuse.
+enfant-f|J'ai demandé une pause.
+maman|Oui.
+maman|Tu t'es assise.
+maman|Les mains sont posées ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1790,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Violette pose les mains. Maman reste près d'elle.</t>
+          <t>Victorina pose les mains. Maman reste près d'elle. On sent encore le chocolat ? Oui. Il est tiède. Les assiettes attendent. Le coussin n'est plus froissé. Il a repris sa forme ronde. Tu restes contre moi ? Oui, maman. La sonnette n'a pas encore sonné. Le salon est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1930,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Violette pose les mains. Maman reste près d'elle.</t>
+          <t>narrateur|Victorina pose les mains.
+narrateur|Maman reste près d'elle.
+maman|On sent encore le chocolat ?
+enfant-f|Oui.
+enfant-f|Il est tiède.
+maman|Les assiettes attendent.
+narrateur|Le coussin n'est plus froissé.
+narrateur|Il a repris sa forme ronde.
+maman|Tu restes contre moi ?
+enfant-f|Oui, maman.
+narrateur|La sonnette n'a pas encore sonné.
+narrateur|Le salon est calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1969,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai demandé une pause. J'étais nerveuse. Bravo. Tu as fait du bon travail. Le gâteau sent encore un peu le chocolat. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2109,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai demandé une pause.
+enfant-f|J'étais nerveuse.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le gâteau sent encore un peu le chocolat.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2174,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le gâteau sent le chocolat. Il est encore un peu chaud. Trois assiettes attendent sur la table. Les fourchettes brillent à côté. La sonnette va bientôt sonner. Les cousins arrivent tout à l'heure. Le gâteau sent bon, Victorina. Il sent le chocolat. Oui. Il est encore tiède. Un napperon blanc est sous le plat. Il a de petits trous. Comme de la dentelle. Tu as vu les assiettes ? Il y en a trois. Oui. Pour plus tard. En ce moment, Victorina attend dans le salon. Elle est sur le canapé. Ses jambes bougent. Ses mains froissent le coussin. Le coussin fait un bruit de tissu. Je suis nerveuse. Mes jambes bougent. Je t'écoute. Nerveux, ce n'est pas vilain. On peut demander une pause. Je veux une pause. Oui, Victorina. On s'assoit. Elle s'assoit près de maman. Elle pose les pieds au tapis. Les pieds sont posés. Tu souffles avec moi ? Oui, maman. Victorina souffle. Les jambes se calment. Les mains laissent le coussin. Une pause, c'est bien. Bravo, Victorina. C'est du bon travail. Tu as demandé la pause ? Oui. Je suis nerveuse. Tu as nommé. Tu t'es assise. Le gâteau sent encore le chocolat. Les assiettes attendent, toutes calmes. La sonnette n'a pas sonné. On a le temps. Mes mains sont posées. Oui. Elles sont douces, maintenant. Tu restes près de moi ? Oui, maman. Le napperon blanc ne bouge plus. Une miette de chocolat brille sur le plat. On la laisse pour plus tard. Le gâteau est tiède. Oui. Comme tes mains. Victorina pose les mains sur ses genoux. Le canapé est mou sous elle. On attend ensemble. Ensemble. Oui.</t>
+          <t>Le gâteau sent le chocolat. Il est encore un peu chaud. Trois assiettes attendent sur la table. Les fourchettes brillent à côté. La sonnette va bientôt sonner. Les cousins arrivent tout à l'heure. Le gâteau sent bon, Victorina. Il sent le chocolat. Oui. Il est encore tiède. Un napperon blanc est sous le plat. Il a de petits trous. Comme de la dentelle. Tu as vu les assiettes ? Il y en a trois. Oui. Pour plus tard. En ce moment, Victorina attend dans le salon. Elle est sur le canapé. Ses jambes bougent. Ses mains froissent le coussin. Le coussin fait un bruit de tissu. Je suis nerveuse. Mes jambes bougent. Je t'écoute. Nerveux, ce n'est pas vilain. On peut demander une pause. Je veux une pause. Oui, Victorina. On s'assoit. Elle s'assoit près de maman. Elle pose les pieds au tapis. Les pieds sont posés. Tu souffles avec moi ? Oui, maman. Victorina souffle. Les jambes se calment. Les mains laissent le coussin. Une pause, c'est bien. Bravo, Victorina. Tu as demandé la pause ? Oui. Je suis nerveuse. Tu as nommé. Tu t'es assise. Le gâteau sent encore le chocolat. Les assiettes attendent, toutes calmes. La sonnette n'a pas sonné. On a le temps. Mes mains sont posées. Oui. Elles sont douces, maintenant. Tu restes près de moi ? Oui, maman. Le napperon blanc ne bouge plus. Une miette de chocolat brille sur le plat. On la laisse pour plus tard. Le gâteau est tiède. Oui. Comme tes mains. Victorina pose les mains sur ses genoux. Le canapé est mou sous elle. On attend ensemble. Ensemble. Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Violette attend dans le salon. Des cousins vont arriver. Ses jambes bougent. Ses mains froissent le coussin. Violette dit : je suis nerveuse. Maman l'écoute. Maman dit : on peut demander une pause. Violette dit : je veux une pause. Elle s'assoit près de maman. Elle souffle. Les jambes se calment. Maman dit : &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;, ce n'est pas vilain. Une pause, c'est bien.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le gâteau sent le chocolat. Il est encore un peu chaud. Trois assiettes attendent sur la table. Les fourchettes brillent à côté. La sonnette va bientôt sonner. Les cousins arrivent tout à l'heure. Le gâteau sent bon, Victorina. Il sent le chocolat. Oui. Il est encore tiède. Un napperon blanc est sous le plat. Il a de petits trous. Comme de la dentelle. Tu as vu les assiettes ? Il y en a trois. Oui. Pour plus tard. En ce moment, Victorina attend dans le salon. Elle est sur le canapé. Ses jambes bougent. Ses mains froissent le coussin. Le coussin fait un bruit de tissu. Je suis nerveuse. Mes jambes bougent. Je t'écoute. Nerveux, ce n'est pas vilain. On peut demander une pause. Je veux une pause. Oui, Victorina. On s'assoit. Elle s'assoit près de maman. Elle pose les pieds au tapis. Les pieds sont posés. Tu souffles avec moi ? Oui, maman. Victorina souffle. Les jambes se calment. Les mains laissent le coussin. Une pause, c'est bien. Bravo, Victorina. Tu as demandé la pause ? Oui. Je suis nerveuse. Tu as nommé. Tu t'es assise. Le gâteau sent encore le chocolat. Les assiettes attendent, toutes calmes. La sonnette n'a pas sonné. On a le temps. Mes mains sont posées. Oui. Elles sont douces, maintenant. Tu restes près de moi ? Oui, maman. Le napperon blanc ne bouge plus. Une miette de chocolat brille sur le plat. On la laisse pour plus tard. Le gâteau est tiède. Oui. Comme tes mains. Victorina pose les mains sur ses genoux. Le canapé est mou sous elle. On attend ensemble. Ensemble. Oui.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1364,7 +1364,6 @@
 narrateur|Les mains laissent le coussin.
 maman|Une pause, c'est bien.
 maman|Bravo, Victorina.
-maman|C'est du bon travail.
 maman|Tu as demandé la pause ?
 enfant-f|Oui.
 enfant-f|Je suis nerveuse.
@@ -1426,7 +1425,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Violette n'arrive pas à tenir. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina n'arrive pas à tenir. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1581,7 +1580,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1606,12 +1604,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a nommé : nerveuse. Nerveux, on peut le dire. Elle a demandé une pause. Elle s'est assise. Bravo, Victorina. Tu as demandé une pause. C'est du bon travail. Je suis nerveuse. J'ai demandé une pause. Oui. Tu t'es assise. Les mains sont posées ? Oui, maman.</t>
+          <t>Victorina a nommé : nerveuse. Nerveux, on peut le dire. Elle a demandé une pause. Elle s'est assise. Bravo, Victorina. Tu as demandé une pause. Je suis nerveuse. J'ai demandé une pause. Oui. Tu t'es assise. Les mains sont posées ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Violette a nommé : nerveuse. Elle a demandé une &lt;emphasis level="moderate"&gt;pause&lt;/emphasis&gt;. Elle s'est assise.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a nommé : nerveuse. Nerveux, on peut le dire. Elle a demandé une pause. Elle s'est assise. Bravo, Victorina. Tu as demandé une pause. Je suis nerveuse. J'ai demandé une pause. Oui. Tu t'es assise. Les mains sont posées ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1756,7 +1754,6 @@
 narrateur|Elle s'est assise.
 maman|Bravo, Victorina.
 maman|Tu as demandé une pause.
-maman|C'est du bon travail.
 enfant-f|Je suis nerveuse.
 enfant-f|J'ai demandé une pause.
 maman|Oui.
@@ -1765,7 +1762,6 @@
 enfant-f|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,7 +1791,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Violette pose les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Maman reste près d'elle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina pose les mains. Maman reste près d'elle. On sent encore le chocolat ? Oui. Il est tiède. Les assiettes attendent. Le coussin n'est plus froissé. Il a repris sa forme ronde. Tu restes contre moi ? Oui, maman. La sonnette n'a pas encore sonné. Le salon est calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1944,7 +1940,6 @@
 narrateur|Le salon est calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,12 +1964,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai demandé une pause. J'étais nerveuse. Bravo. Tu as fait du bon travail. Le gâteau sent encore un peu le chocolat. L'histoire est finie.</t>
+          <t>J'ai demandé une pause. J'étais nerveuse. Bravo. Le gâteau sent encore un peu le chocolat.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai demandé une pause. J'étais nerveuse. Bravo. Le gâteau sent encore un peu le chocolat.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2112,12 +2107,9 @@
           <t>enfant-f|J'ai demandé une pause.
 enfant-f|J'étais nerveuse.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le gâteau sent encore un peu le chocolat.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le gâteau sent encore un peu le chocolat.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2136,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2181,6 +2173,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Violette, maman</t>
+          <t>Victorina, maman</t>
         </is>
       </c>
     </row>
